--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -449,10 +449,10 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="62" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="46" customWidth="1" min="11" max="11"/>
   </cols>
@@ -485,30 +485,45 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>buffId</t>
+          <t>statEffects</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>stackBehavior</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>maxStack</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>triggerCondition</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>healthThresholdPercent</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>intervalSeconds</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -547,25 +562,40 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -599,14 +629,25 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Buff_DefenseUp_Passive</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
+          <t>defensePowerPercent:10</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
+      <c r="K3" s="3" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="M3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -636,14 +677,25 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Buff_MoveSpeedUpPassive</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="n"/>
-      <c r="I4" s="3" t="n"/>
+          <t>moveSpeedFlat:1</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="n"/>
+      <c r="L4" s="3" t="n"/>
+      <c r="M4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -673,18 +725,29 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Buff_AttackSpeedUp_Triggered</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+          <t>attackSpeedPercent:30</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>OnHitTaken</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n"/>
-      <c r="I5" s="3" t="n"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
+      <c r="K5" s="3" t="n"/>
+      <c r="L5" s="3" t="n"/>
+      <c r="M5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -714,18 +777,29 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Buff_MoveSpeedUp_OnAttack</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+          <t>moveSpeedPercent:20</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>OnDamageDealt</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n"/>
-      <c r="I6" s="3" t="n"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr">
+      <c r="K6" s="3" t="n"/>
+      <c r="L6" s="3" t="n"/>
+      <c r="M6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t>OnDamageDealt는 아직 전투 시스템에 연결 전이라 실전투에서 발동하지 않음</t>
         </is>
@@ -759,16 +833,27 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Buff_MoveSpeedUp_LowHealth</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
+          <t>moveSpeedPercent:50</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
+      <c r="K7" s="3" t="n">
         <v>50</v>
       </c>
-      <c r="I7" s="3" t="n"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="L7" s="3" t="n"/>
+      <c r="M7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
@@ -797,29 +882,39 @@
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="n"/>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="inlineStr"/>
       <c r="I8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr"/>
+      <c r="K8" s="3" t="n"/>
+      <c r="L8" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="M8" s="3" t="inlineStr">
         <is>
           <t>HELLO WORLD!</t>
         </is>
       </c>
-      <c r="K8" s="3" t="inlineStr">
+      <c r="N8" s="3" t="inlineStr">
         <is>
           <t>동작 확인용 테스트 효과</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="B3:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>=ComboBox!$A$2:$A$5</formula1>
     </dataValidation>
     <dataValidation sqref="G3:G200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=ComboBox!$B$2:$B$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="H3:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=ComboBox!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -832,11 +927,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -850,6 +946,11 @@
           <t>triggerCondition</t>
         </is>
       </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>stackBehavior</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -862,6 +963,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>RefreshDuration</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -874,6 +980,11 @@
           <t>OnHitTaken</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -884,6 +995,11 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ignore</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R9"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -446,7 +446,7 @@
     <col width="20" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="30.09765625" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="34.8" customFormat="1" customHeight="1" s="7">
@@ -525,17 +525,22 @@
           <t>thresholdValue</t>
         </is>
       </c>
-      <c r="P1" s="3" t="inlineStr">
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>radius</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
         <is>
           <t>intervalSeconds</t>
         </is>
       </c>
-      <c r="Q1" s="3" t="inlineStr">
+      <c r="R1" s="3" t="inlineStr">
         <is>
           <t>message</t>
         </is>
       </c>
-      <c r="R1" s="3" t="inlineStr">
+      <c r="S1" s="3" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -617,17 +622,22 @@
           <t>float</t>
         </is>
       </c>
-      <c r="P2" s="10" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
       <c r="Q2" s="10" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="R2" s="10" t="inlineStr">
+      <c r="S2" s="10" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -685,9 +695,9 @@
         </is>
       </c>
       <c r="M3" s="1" t="n"/>
-      <c r="P3" s="1" t="n"/>
       <c r="Q3" s="1" t="n"/>
       <c r="R3" s="1" t="n"/>
+      <c r="S3" s="1" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -741,9 +751,9 @@
         </is>
       </c>
       <c r="M4" s="1" t="n"/>
-      <c r="P4" s="1" t="n"/>
       <c r="Q4" s="1" t="n"/>
       <c r="R4" s="1" t="n"/>
+      <c r="S4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -801,9 +811,9 @@
         </is>
       </c>
       <c r="M5" s="1" t="n"/>
-      <c r="P5" s="1" t="n"/>
       <c r="Q5" s="1" t="n"/>
       <c r="R5" s="1" t="n"/>
+      <c r="S5" s="1" t="n"/>
     </row>
     <row r="6" ht="34.8" customHeight="1">
       <c r="A6" s="1" t="inlineStr">
@@ -861,9 +871,9 @@
         </is>
       </c>
       <c r="M6" s="1" t="n"/>
-      <c r="P6" s="1" t="n"/>
       <c r="Q6" s="1" t="n"/>
-      <c r="R6" s="1" t="inlineStr">
+      <c r="R6" s="1" t="n"/>
+      <c r="S6" s="1" t="inlineStr">
         <is>
           <t>OnDamageDealt는 아직 전투 시스템에 연결 전이라 실전투에서 발동하지 않음</t>
         </is>
@@ -933,9 +943,9 @@
       <c r="O7" t="n">
         <v>50</v>
       </c>
-      <c r="P7" s="1" t="n"/>
       <c r="Q7" s="1" t="n"/>
       <c r="R7" s="1" t="n"/>
+      <c r="S7" s="1" t="n"/>
     </row>
     <row r="8" ht="52.2" customHeight="1">
       <c r="A8" s="1" t="inlineStr">
@@ -981,15 +991,15 @@
         </is>
       </c>
       <c r="M8" s="1" t="n"/>
-      <c r="P8" s="1" t="n">
+      <c r="Q8" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="Q8" s="1" t="inlineStr">
+      <c r="R8" s="1" t="inlineStr">
         <is>
           <t>HELLO WORLD!</t>
         </is>
       </c>
-      <c r="R8" s="1" t="inlineStr">
+      <c r="S8" s="1" t="inlineStr">
         <is>
           <t>동작 확인용 테스트 효과</t>
         </is>
@@ -1051,20 +1061,135 @@
         </is>
       </c>
       <c r="M9" s="1" t="n"/>
-      <c r="P9" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1" t="n"/>
-      <c r="R9" s="1" t="inlineStr">
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n"/>
+      <c r="S9" s="1" t="inlineStr">
         <is>
           <t>회피키(기본 Space) 입력 시 발동</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UE_LightSaber</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TriggeredBuffUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>광자 가속</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>기본 공격 시 {0}초간 공격 속도가 {1}% 증가합니다. (최대 {2}스택)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5;6;5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>attackSpeedPercent:6</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Stack</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>OnDamageDealt</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>기본 공격 적중마다 스택, 스택될 때마다 지속시간 갱신(PlayerBuffManager 기본 동작)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>UE_HasteAura</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>FieldAuraUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>영역: 가속화</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>반경 {0}유닛 안의 플레이어들의 이동 속도가 {1}% 증가합니다.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>10;30</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>moveSpeedPercent:30</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>10</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>아직 어떤 아이템에도 배정하지 않음(효과만 우선 제작)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="6">
     <dataValidation sqref="B3:B200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
-      <formula1>=ComboBox!$A$2:$A$5</formula1>
+      <formula1>=ComboBox!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="J3:J200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="잘못된 값" error="목록에 없는 값입니다. 드롭다운에서 선택해주세요." type="list">
       <formula1>=ComboBox!$B$2:$B$7</formula1>
@@ -1221,21 +1346,26 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>FieldAuraUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>OnKill</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>DefensePower</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>PeriodicLogUniqueEffectSO</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>OnKill</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>DefensePower</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
       <c r="B6" t="inlineStr">
         <is>
           <t>OnDamageDealt</t>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="Rbb1f4c91ef444e51"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="Rbcbf42cdd6cc4557"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="R3565a67703844b73"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="R5cfed1ad9f7944b9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3128,6 +3128,239 @@
         <x:v>지원 중인 처치 발동 버프</x:v>
       </x:c>
     </x:row>
+    <x:row r="48">
+      <x:c r="A48" t="str">
+        <x:v>UE_PhaseOrchid</x:v>
+      </x:c>
+      <x:c r="B48" t="str">
+        <x:v>PassiveBuffUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C48" t="str">
+        <x:v>허공 개화</x:v>
+      </x:c>
+      <x:c r="D48" t="str">
+        <x:v>장착 중 치명타 확률이 {0}, 스킬 범위가 {1}% 증가합니다.</x:v>
+      </x:c>
+      <x:c r="E48" t="str">
+        <x:v>8;10</x:v>
+      </x:c>
+      <x:c r="F48" t="str">
+        <x:v>critRateFlat:8;skillRangePercent:10</x:v>
+      </x:c>
+      <x:c r="G48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H48" t="str">
+        <x:v>Ignore</x:v>
+      </x:c>
+      <x:c r="I48" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J48"/>
+      <x:c r="K48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48" t="str">
+        <x:v>ShareCooldown</x:v>
+      </x:c>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+      <x:c r="O48"/>
+      <x:c r="P48"/>
+      <x:c r="Q48"/>
+      <x:c r="R48"/>
+      <x:c r="S48" t="str">
+        <x:v>지속 패시브: 정밀 조준 특화</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" t="str">
+        <x:v>UE_GlassCannon</x:v>
+      </x:c>
+      <x:c r="B49" t="str">
+        <x:v>PassiveBuffUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C49" t="str">
+        <x:v>유리 심장</x:v>
+      </x:c>
+      <x:c r="D49" t="str">
+        <x:v>장착 중 공격력이 {0}% 증가하지만 방어력이 {1}% 감소합니다.</x:v>
+      </x:c>
+      <x:c r="E49" t="str">
+        <x:v>18;12</x:v>
+      </x:c>
+      <x:c r="F49" t="str">
+        <x:v>attackPowerPercent:18;defensePowerPercent:-12</x:v>
+      </x:c>
+      <x:c r="G49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H49" t="str">
+        <x:v>Ignore</x:v>
+      </x:c>
+      <x:c r="I49" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J49"/>
+      <x:c r="K49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49" t="str">
+        <x:v>ShareCooldown</x:v>
+      </x:c>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+      <x:c r="O49"/>
+      <x:c r="P49"/>
+      <x:c r="Q49"/>
+      <x:c r="R49"/>
+      <x:c r="S49" t="str">
+        <x:v>지속 패시브: 고출력과 방어 손실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" t="str">
+        <x:v>UE_Incinerator</x:v>
+      </x:c>
+      <x:c r="B50" t="str">
+        <x:v>PassiveBuffUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C50" t="str">
+        <x:v>소각 압력</x:v>
+      </x:c>
+      <x:c r="D50" t="str">
+        <x:v>장착 중 공격력이 {0}%, 화염 피해 보너스가 {1} 증가하지만 방어력이 {2}% 감소합니다.</x:v>
+      </x:c>
+      <x:c r="E50" t="str">
+        <x:v>8;12;6</x:v>
+      </x:c>
+      <x:c r="F50" t="str">
+        <x:v>attackPowerPercent:8;fireBonusFlat:12;defensePowerPercent:-6</x:v>
+      </x:c>
+      <x:c r="G50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H50" t="str">
+        <x:v>Ignore</x:v>
+      </x:c>
+      <x:c r="I50" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J50"/>
+      <x:c r="K50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50" t="str">
+        <x:v>ShareCooldown</x:v>
+      </x:c>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+      <x:c r="O50"/>
+      <x:c r="P50"/>
+      <x:c r="Q50"/>
+      <x:c r="R50"/>
+      <x:c r="S50" t="str">
+        <x:v>지속 패시브: 화염 특화와 방어 손실</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" t="str">
+        <x:v>UE_Apocalypse</x:v>
+      </x:c>
+      <x:c r="B51" t="str">
+        <x:v>StatThresholdBuffUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C51" t="str">
+        <x:v>최후의 봉인</x:v>
+      </x:c>
+      <x:c r="D51" t="str">
+        <x:v>체력이 {0}% 이하일 때 공격력이 {1}%, 관통력이 {2} 증가합니다.</x:v>
+      </x:c>
+      <x:c r="E51" t="str">
+        <x:v>50;20;15</x:v>
+      </x:c>
+      <x:c r="F51" t="str">
+        <x:v>attackPowerPercent:20;penetrationFlat:15</x:v>
+      </x:c>
+      <x:c r="G51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H51" t="str">
+        <x:v>Ignore</x:v>
+      </x:c>
+      <x:c r="I51" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J51"/>
+      <x:c r="K51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51" t="str">
+        <x:v>ShareCooldown</x:v>
+      </x:c>
+      <x:c r="M51" t="str">
+        <x:v>CurrentHealthPercent</x:v>
+      </x:c>
+      <x:c r="N51" t="str">
+        <x:v>LessOrEqual</x:v>
+      </x:c>
+      <x:c r="O51" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="P51"/>
+      <x:c r="Q51"/>
+      <x:c r="R51"/>
+      <x:c r="S51" t="str">
+        <x:v>실제 연결된 저체력 조건부 공격 버프</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" t="str">
+        <x:v>UE_ConversationStarter</x:v>
+      </x:c>
+      <x:c r="B52" t="str">
+        <x:v>TriggeredBuffUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C52" t="str">
+        <x:v>반론 차단</x:v>
+      </x:c>
+      <x:c r="D52" t="str">
+        <x:v>피격 시 {0}초간 공격 속도가 {1}%, 방어력이 {2}% 증가합니다. (쿨타임 {3}초)</x:v>
+      </x:c>
+      <x:c r="E52" t="str">
+        <x:v>4;20;15;10</x:v>
+      </x:c>
+      <x:c r="F52" t="str">
+        <x:v>attackSpeedPercent:20;defensePowerPercent:15</x:v>
+      </x:c>
+      <x:c r="G52" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="H52" t="str">
+        <x:v>RefreshDuration</x:v>
+      </x:c>
+      <x:c r="I52" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J52" t="str">
+        <x:v>OnHitTaken</x:v>
+      </x:c>
+      <x:c r="K52" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="L52" t="str">
+        <x:v>ShareCooldown</x:v>
+      </x:c>
+      <x:c r="M52"/>
+      <x:c r="N52"/>
+      <x:c r="O52"/>
+      <x:c r="P52"/>
+      <x:c r="Q52"/>
+      <x:c r="R52"/>
+      <x:c r="S52" t="str">
+        <x:v>실제 연결된 피격 발동 버프</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="R3565a67703844b73"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="R5cfed1ad9f7944b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="R6a59d224f17c4593"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="R3a5e1f16c2384093"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -77,7 +77,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="14">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
@@ -110,6 +110,13 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -184,6 +191,23 @@
     </x:indexedColors>
   </x:colors>
 </x:styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<xfpb:FeaturePropertyBags xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <xfpb:bag type="Checkbox"/>
+  <xfpb:bag type="XFControls">
+    <xfpb:bagId k="CellControl">0</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplement">
+    <xfpb:bagId k="XFControls">1</xfpb:bagId>
+  </xfpb:bag>
+  <xfpb:bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <xfpb:a k="MappedFeaturePropertyBags">
+      <xfpb:bagId>2</xfpb:bagId>
+    </xfpb:a>
+  </xfpb:bag>
+</xfpb:FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,6 +441,8 @@
     <x:col min="14" max="14" width="18" customWidth="1"/>
     <x:col min="15" max="15" width="16" customWidth="1"/>
     <x:col min="16" max="16" width="14" customWidth="1"/>
+    <x:col min="20" max="20" width="20" hidden="0" customWidth="1"/>
+    <x:col min="21" max="21" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="7" customFormat="1" ht="34.79999923706055" customHeight="1">
@@ -515,6 +541,12 @@
           <x:t xml:space="preserve">note</x:t>
         </x:is>
       </x:c>
+      <x:c r="T1" t="str">
+        <x:v>persistStackOnItem</x:v>
+      </x:c>
+      <x:c r="U1" t="str">
+        <x:v>targetEnemies</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" s="9" customFormat="1">
       <x:c r="A2" s="10" t="inlineStr">
@@ -611,6 +643,12 @@
         <x:is>
           <x:t xml:space="preserve">string</x:t>
         </x:is>
+      </x:c>
+      <x:c r="T2" t="str">
+        <x:v>bool</x:v>
+      </x:c>
+      <x:c r="U2" t="str">
+        <x:v>bool</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -668,6 +706,12 @@
       <x:c r="Q3" s="1" t="n"/>
       <x:c r="R3" s="1" t="n"/>
       <x:c r="S3" s="1" t="n"/>
+      <x:c r="T3" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U3" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="1" t="inlineStr">
@@ -724,6 +768,12 @@
       <x:c r="Q4" s="1" t="n"/>
       <x:c r="R4" s="1" t="n"/>
       <x:c r="S4" s="1" t="n"/>
+      <x:c r="T4" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U4" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="1" t="inlineStr">
@@ -784,6 +834,12 @@
       <x:c r="Q5" s="1" t="n"/>
       <x:c r="R5" s="1" t="n"/>
       <x:c r="S5" s="1" t="n"/>
+      <x:c r="T5" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U5" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="34.79999923706055" customHeight="1">
       <x:c r="A6" s="1" t="inlineStr">
@@ -848,6 +904,12 @@
           <x:t xml:space="preserve">OnDamageDealt는 아직 전투 시스템에 연결 전이라 실전투에서 발동하지 않음</x:t>
         </x:is>
       </x:c>
+      <x:c r="T6" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U6" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="34.79999923706055" customHeight="1">
       <x:c r="A7" s="1" t="inlineStr">
@@ -916,6 +978,12 @@
       <x:c r="Q7" s="1" t="n"/>
       <x:c r="R7" s="1" t="n"/>
       <x:c r="S7" s="1" t="n"/>
+      <x:c r="T7" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U7" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="52.20000076293945" customHeight="1">
       <x:c r="A8" s="1" t="inlineStr">
@@ -974,6 +1042,12 @@
           <x:t xml:space="preserve">동작 확인용 테스트 효과</x:t>
         </x:is>
       </x:c>
+      <x:c r="T8" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U8" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="69.5999984741211" customHeight="1">
       <x:c r="A9" s="1" t="inlineStr">
@@ -1040,6 +1114,12 @@
           <x:t xml:space="preserve">회피키(기본 Space) 입력 시 발동</x:t>
         </x:is>
       </x:c>
+      <x:c r="T9" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U9" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" t="inlineStr">
@@ -1104,6 +1184,12 @@
           <x:t xml:space="preserve">기본 공격 적중마다 스택, 스택될 때마다 지속시간 갱신(PlayerBuffManager 기본 동작)</x:t>
         </x:is>
       </x:c>
+      <x:c r="T10" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U10" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" t="inlineStr">
@@ -1158,6 +1244,12 @@
           <x:t xml:space="preserve">아직 어떤 아이템에도 배정하지 않음(효과만 우선 제작)</x:t>
         </x:is>
       </x:c>
+      <x:c r="T11" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U11" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="1" t="inlineStr">
@@ -1207,6 +1299,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T12" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U12" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="34.79999923706055" customHeight="1">
       <x:c r="A13" s="1" t="inlineStr">
@@ -1271,6 +1369,12 @@
       <x:c r="O13" t="n">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="T13" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U13" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="1" t="inlineStr">
@@ -1316,6 +1420,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T14" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U14" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="1" t="inlineStr">
@@ -1370,6 +1480,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T15" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U15" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" t="inlineStr">
@@ -1431,6 +1547,12 @@
           <x:t xml:space="preserve">피격 시 공속 증가</x:t>
         </x:is>
       </x:c>
+      <x:c r="T16" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U16" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" t="inlineStr">
@@ -1500,6 +1622,12 @@
           <x:t xml:space="preserve">저체력 공격/관통 증가</x:t>
         </x:is>
       </x:c>
+      <x:c r="T17" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U17" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" t="inlineStr">
@@ -1561,6 +1689,12 @@
           <x:t xml:space="preserve">피격 시 방어 증가</x:t>
         </x:is>
       </x:c>
+      <x:c r="T18" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U18" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" t="inlineStr">
@@ -1622,6 +1756,12 @@
           <x:t xml:space="preserve">임시 고유효과: 보호막 대신 기존 발동 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T19" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U19" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" t="inlineStr">
@@ -1678,6 +1818,12 @@
           <x:t xml:space="preserve">공격 증가/방어 감소</x:t>
         </x:is>
       </x:c>
+      <x:c r="T20" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U20" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" t="inlineStr">
@@ -1739,6 +1885,12 @@
           <x:t xml:space="preserve">임시 고유효과: 회복 대신 치명타 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T21" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U21" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" t="inlineStr">
@@ -1795,6 +1947,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T22" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U22" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" t="inlineStr">
@@ -1859,6 +2017,12 @@
       <x:c r="O23" t="n">
         <x:v>40</x:v>
       </x:c>
+      <x:c r="T23" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U23" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" t="inlineStr">
@@ -1910,6 +2074,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T24" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U24" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" t="inlineStr">
@@ -1971,6 +2141,12 @@
           <x:t xml:space="preserve">임시 고유효과: 보호막 대신 기존 방어 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T25" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U25" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" t="inlineStr">
@@ -2022,6 +2198,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T26" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U26" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="inlineStr">
@@ -2083,6 +2265,12 @@
           <x:t xml:space="preserve">임시 고유효과: 장비 설명의 공격 궤적 회피 효과 구현 전까지 사용</x:t>
         </x:is>
       </x:c>
+      <x:c r="T27" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U27" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" t="inlineStr">
@@ -2134,6 +2322,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T28" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U28" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" t="inlineStr">
@@ -2195,6 +2389,12 @@
           <x:t xml:space="preserve">임시 고유효과: 이동 반전 효과 구현 전까지 사용</x:t>
         </x:is>
       </x:c>
+      <x:c r="T29" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U29" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" t="inlineStr">
@@ -2259,6 +2459,12 @@
       <x:c r="O30" t="n">
         <x:v>30</x:v>
       </x:c>
+      <x:c r="T30" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U30" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" t="inlineStr">
@@ -2310,6 +2516,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T31" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U31" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" t="inlineStr">
@@ -2371,6 +2583,12 @@
           <x:t xml:space="preserve">회복 대신 기존 방어 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T32" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U32" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" t="inlineStr">
@@ -2422,6 +2640,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T33" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U33" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" t="inlineStr">
@@ -2478,6 +2702,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T34" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U34" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" t="inlineStr">
@@ -2529,6 +2759,12 @@
           <x:t xml:space="preserve">신규 행운 효과. 중복 보유 비누적</x:t>
         </x:is>
       </x:c>
+      <x:c r="T35" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U35" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" t="inlineStr">
@@ -2580,6 +2816,12 @@
           <x:t xml:space="preserve">ShareCooldown</x:t>
         </x:is>
       </x:c>
+      <x:c r="T36" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U36" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" t="inlineStr">
@@ -2641,6 +2883,12 @@
           <x:t xml:space="preserve">회복 대신 영구 누적 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T37" s="13" t="b">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="U37" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" t="inlineStr">
@@ -2702,6 +2950,12 @@
           <x:t xml:space="preserve">마나 회복 대신 기존 기동 버프로 구현</x:t>
         </x:is>
       </x:c>
+      <x:c r="T38" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U38" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" t="inlineStr">
@@ -2752,6 +3006,12 @@
         <x:is>
           <x:t xml:space="preserve">적 대상 디버프 - FieldAuraUniqueEffectSO.targetEnemies를 true로 수동 설정 필요(코드 신규 필드, 엑셀 컬럼 없음)</x:t>
         </x:is>
+      </x:c>
+      <x:c r="T39" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U39" s="13" t="b">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -2803,6 +3063,12 @@
       <x:c r="R40"/>
       <x:c r="S40" t="str">
         <x:v>지원 중인 저체력 조건형 공격 버프</x:v>
+      </x:c>
+      <x:c r="T40" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U40" s="13" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -2851,6 +3117,12 @@
       <x:c r="S41" t="str">
         <x:v>지원 중인 치명타 발동 버프</x:v>
       </x:c>
+      <x:c r="T41" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U41" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" t="str">
@@ -2896,6 +3168,12 @@
       <x:c r="S42" t="str">
         <x:v>지속 패시브 공격 특화 효과</x:v>
       </x:c>
+      <x:c r="T42" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U42" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" t="str">
@@ -2943,6 +3221,12 @@
       <x:c r="S43" t="str">
         <x:v>지원 중인 처치 발동 버프</x:v>
       </x:c>
+      <x:c r="T43" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U43" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" t="str">
@@ -2988,6 +3272,12 @@
       <x:c r="S44" t="str">
         <x:v>지속 패시브 연사 특화 효과</x:v>
       </x:c>
+      <x:c r="T44" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U44" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" t="str">
@@ -3035,6 +3325,12 @@
       <x:c r="S45" t="str">
         <x:v>지원 중인 치명타 발동 버프</x:v>
       </x:c>
+      <x:c r="T45" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U45" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" t="str">
@@ -3080,6 +3376,12 @@
       <x:c r="S46" t="str">
         <x:v>지속 패시브 정밀 사격 효과</x:v>
       </x:c>
+      <x:c r="T46" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U46" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" t="str">
@@ -3127,6 +3429,12 @@
       <x:c r="S47" t="str">
         <x:v>지원 중인 처치 발동 버프</x:v>
       </x:c>
+      <x:c r="T47" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U47" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" t="str">
@@ -3172,6 +3480,12 @@
       <x:c r="S48" t="str">
         <x:v>지속 패시브: 정밀 조준 특화</x:v>
       </x:c>
+      <x:c r="T48" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U48" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" t="str">
@@ -3217,6 +3531,12 @@
       <x:c r="S49" t="str">
         <x:v>지속 패시브: 고출력과 방어 손실</x:v>
       </x:c>
+      <x:c r="T49" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U49" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" t="str">
@@ -3262,6 +3582,12 @@
       <x:c r="S50" t="str">
         <x:v>지속 패시브: 화염 특화와 방어 손실</x:v>
       </x:c>
+      <x:c r="T50" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U50" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" t="str">
@@ -3312,6 +3638,12 @@
       <x:c r="R51"/>
       <x:c r="S51" t="str">
         <x:v>실제 연결된 저체력 조건부 공격 버프</x:v>
+      </x:c>
+      <x:c r="T51" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U51" s="13" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -3359,6 +3691,12 @@
       <x:c r="R52"/>
       <x:c r="S52" t="str">
         <x:v>실제 연결된 피격 발동 버프</x:v>
+      </x:c>
+      <x:c r="T52" s="13" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U52" s="13" t="b">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="38" customWidth="1" style="13" min="1" max="1"/>
@@ -3905,6 +3905,81 @@
         <v>0</v>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" spans="1:21" ns1:dyDescent="0.4">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>UE_LowManaRecovery</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>StatThresholdBuffUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>절전 모드</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>현재 마나가 최대 마나의 {0}% 이하일 때 마나 재생이 {1}% 증가합니다.</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>25;30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>mpRegenPercent:30</t>
+        </is>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I53">
+        <v>1</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>CurrentManaPercent</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>LessOrEqual</t>
+        </is>
+      </c>
+      <c r="O53">
+        <v>25</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>저마나 재생 보조. 최대 마나와 즉시 회복량은 변경하지 않음.</t>
+        </is>
+      </c>
+      <c r="T53" t="b">
+        <v>0</v>
+      </c>
+      <c r="U53" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="38" customWidth="1" style="13" min="1" max="1"/>
@@ -3905,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="53" spans="1:21" ns1:dyDescent="0.4">
+    <row r="53">
       <c r="A53" t="inlineStr">
         <is>
           <t>UE_LowManaRecovery</t>
@@ -3936,7 +3936,7 @@
           <t>mpRegenPercent:30</t>
         </is>
       </c>
-      <c r="G53">
+      <c r="G53" t="n">
         <v>0</v>
       </c>
       <c r="H53" t="inlineStr">
@@ -3944,10 +3944,10 @@
           <t>Ignore</t>
         </is>
       </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="K53">
+      <c r="I53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="inlineStr">
@@ -3965,7 +3965,7 @@
           <t>LessOrEqual</t>
         </is>
       </c>
-      <c r="O53">
+      <c r="O53" t="n">
         <v>25</v>
       </c>
       <c r="S53" t="inlineStr">
@@ -3979,6 +3979,338 @@
       <c r="U53" t="b">
         <v>0</v>
       </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TriggeredBuffUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔여 추력</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회피 사용 후 {0}초간 일반 이동 속도가 {1}% 증가합니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2;20;6</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moveSpeedPercent:20</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RefreshDuration</t>
+        </is>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnDodge</t>
+        </is>
+      </c>
+      <c r="K54">
+        <v>6</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3-B 시제품. 성공 회피가 아닌 회피 상태 진입.</t>
+        </is>
+      </c>
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FieldAuraUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마나 중계</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반경 {0}m 안의 자신과 살아 있는 아군의 마나 재생이 {1}% 증가합니다. 같은 효과는 중첩되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6;15</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mpRegenPercent:15</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ignore</t>
+        </is>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55"/>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55">
+        <v>6</v>
+      </c>
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3-B 시제품. 소지 중 활성, 같은 효과 비중첩.</t>
+        </is>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ArcBladeChainLightning</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChainLightningUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아크 연쇄</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">직접 기본 공격 시 반경 {1}m 내 적 최대 {0}명에게 공격력의 {2}% 전기 피해를 연쇄로 줍니다. 이후 전이는 이전 피해 계수의 {3}%이며, 재사용 대기시간은 {4}초입니다.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3;4;25;80;0.8</t>
+        </is>
+      </c>
+      <c r="F56"/>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56"/>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56"/>
+      <c r="K56">
+        <v>0.8</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_InfernoExtraHit</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfernoExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지옥불 추가타</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근접 기본 공격 적중 시 같은 대상에게 공격력의 {0}% 화염 피해를 추가로 줍니다.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="F57"/>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57"/>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57"/>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_GlassRailExtraHit</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GlassRailExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빙궤 추가타</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라이플 탄 적중 시 같은 대상에게 공격력의 {0}% 냉기 피해를 추가로 줍니다. (발사 후 무기 교체 또는 해제 시에도 유지, 비치명)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F58"/>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58"/>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58"/>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4193,6 +4525,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChainLightningUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>CritRate</t>
@@ -4200,6 +4537,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfernoExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>CritMult</t>
@@ -4207,6 +4549,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GlassRailExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Cdr</t>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V53"/>
+  <dimension ref="A1:V58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="38" customWidth="1" style="13" min="1" max="1"/>
@@ -3980,6 +3980,338 @@
         <v>0</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_DodgeMoveBoost</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TriggeredBuffUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">잔여 추력</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">회피 사용 후 {0}초간 일반 이동 속도가 {1}% 증가합니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2;20;6</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">moveSpeedPercent:20</t>
+        </is>
+      </c>
+      <c r="G54">
+        <v>2</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RefreshDuration</t>
+        </is>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">OnDodge</t>
+        </is>
+      </c>
+      <c r="K54">
+        <v>6</v>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M54"/>
+      <c r="N54"/>
+      <c r="O54"/>
+      <c r="P54"/>
+      <c r="Q54"/>
+      <c r="R54"/>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3-B 시제품. 성공 회피가 아닌 회피 상태 진입.</t>
+        </is>
+      </c>
+      <c r="T54" t="b">
+        <v>0</v>
+      </c>
+      <c r="U54" t="b">
+        <v>0</v>
+      </c>
+      <c r="V54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ManaRelay</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FieldAuraUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">마나 중계</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">반경 {0}m 안의 자신과 살아 있는 아군의 마나 재생이 {1}% 증가합니다. 같은 효과는 중첩되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6;15</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">mpRegenPercent:15</t>
+        </is>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ignore</t>
+        </is>
+      </c>
+      <c r="I55">
+        <v>1</v>
+      </c>
+      <c r="J55"/>
+      <c r="K55">
+        <v>0</v>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M55"/>
+      <c r="N55"/>
+      <c r="O55"/>
+      <c r="P55">
+        <v>6</v>
+      </c>
+      <c r="Q55"/>
+      <c r="R55"/>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">P3-B 시제품. 소지 중 활성, 같은 효과 비중첩.</t>
+        </is>
+      </c>
+      <c r="T55" t="b">
+        <v>0</v>
+      </c>
+      <c r="U55" t="b">
+        <v>0</v>
+      </c>
+      <c r="V55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_ArcBladeChainLightning</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChainLightningUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">아크 연쇄</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">직접 기본 공격 시 반경 {1}m 내 적 최대 {0}명에게 공격력의 {2}% 전기 피해를 연쇄로 줍니다. 이후 전이는 이전 피해 계수의 {3}%이며, 재사용 대기시간은 {4}초입니다.</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3;4;25;80;0.8</t>
+        </is>
+      </c>
+      <c r="F56"/>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56"/>
+      <c r="I56">
+        <v>1</v>
+      </c>
+      <c r="J56"/>
+      <c r="K56">
+        <v>0.8</v>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M56"/>
+      <c r="N56"/>
+      <c r="O56"/>
+      <c r="P56"/>
+      <c r="Q56"/>
+      <c r="R56"/>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T56" t="b">
+        <v>0</v>
+      </c>
+      <c r="U56" t="b">
+        <v>0</v>
+      </c>
+      <c r="V56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_InfernoExtraHit</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfernoExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지옥불 추가타</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">근접 기본 공격 적중 시 같은 대상에게 공격력의 {0}% 화염 피해를 추가로 줍니다.</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20</t>
+        </is>
+      </c>
+      <c r="F57"/>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57"/>
+      <c r="I57">
+        <v>1</v>
+      </c>
+      <c r="J57"/>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M57"/>
+      <c r="N57"/>
+      <c r="O57"/>
+      <c r="P57"/>
+      <c r="Q57"/>
+      <c r="R57"/>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T57" t="b">
+        <v>0</v>
+      </c>
+      <c r="U57" t="b">
+        <v>0</v>
+      </c>
+      <c r="V57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">UE_GlassRailExtraHit</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GlassRailExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">빙궤 추가타</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">라이플 탄 적중 시 같은 대상에게 공격력의 {0}% 냉기 피해를 추가로 줍니다. (발사 후 무기 교체 또는 해제 시에도 유지, 비치명)</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15</t>
+        </is>
+      </c>
+      <c r="F58"/>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58"/>
+      <c r="I58">
+        <v>1</v>
+      </c>
+      <c r="J58"/>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ShareCooldown</t>
+        </is>
+      </c>
+      <c r="M58"/>
+      <c r="N58"/>
+      <c r="O58"/>
+      <c r="P58"/>
+      <c r="Q58"/>
+      <c r="R58"/>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1: 기존 수동 SO와 같은 값. 아이콘/GUID는 유지.</t>
+        </is>
+      </c>
+      <c r="T58" t="b">
+        <v>0</v>
+      </c>
+      <c r="U58" t="b">
+        <v>0</v>
+      </c>
+      <c r="V58"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4193,6 +4525,11 @@
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ChainLightningUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>CritRate</t>
@@ -4200,6 +4537,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfernoExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>CritMult</t>
@@ -4207,6 +4549,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GlassRailExtraHitUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>Cdr</t>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -404,7 +404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V58"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.39999961853027"/>
   <cols>
     <col width="38" customWidth="1" style="13" min="1" max="1"/>
@@ -4312,6 +4312,60 @@
       </c>
       <c r="V58"/>
     </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>UE_SolarGraceShield</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SolarGraceShieldUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>태양의 은혜 보호막</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>체력 {0}% 이상에서 {1}초간 피격되지 않으면 최대 체력의 {2}% 보호막을 {3}초 동안 얻습니다. 보호막은 중첩되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>80;8;15;12</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>UE_NightSwordDodgeStrike</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>DodgePreparedAttackUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>그림자 기습</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>회피 후 다음 기본 공격의 피해가 {0}% 증가합니다.</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4561,6 +4615,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SolarGraceShieldUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>MpRegen</t>
@@ -4568,6 +4627,11 @@
       </c>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>DodgePreparedAttackUniqueEffectSO</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>MaxMana</t>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="R778428098c8a4abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="R550ee761bdf149e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UniqueEffectDefinitions" sheetId="1" r:id="Rb1e110a9af294aad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ComboBox" sheetId="2" r:id="Rfaf28b1969f54261"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4428,6 +4428,48 @@
         <x:v>Debuff</x:v>
       </x:c>
     </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>UE_SingularityDelayedExplosion</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>SingularityDelayedExplosionUniqueEffectSO</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>지연 특이점</x:v>
+      </x:c>
+      <x:c r="D62" t="str">
+        <x:v>유탄이 충돌한 자리에 특이점을 예약해 {0}초 후 반경 {1}m 적에게 공격력의 {2}% 피해를 줍니다. 최대 {3}개까지 유지됩니다.</x:v>
+      </x:c>
+      <x:c r="E62" t="str">
+        <x:v>2;4;100;3</x:v>
+      </x:c>
+      <x:c r="F62"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62"/>
+      <x:c r="J62"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
+      <x:c r="M62"/>
+      <x:c r="N62"/>
+      <x:c r="O62"/>
+      <x:c r="P62"/>
+      <x:c r="Q62"/>
+      <x:c r="R62"/>
+      <x:c r="S62" t="str">
+        <x:v>P6-B: 충돌 위치 고정 지연 폭발. 무기 교체에는 유지하고 소유자 사망·씬 전환·상한 초과 시 취소.</x:v>
+      </x:c>
+      <x:c r="T62" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="U62" s="14" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="V62" t="str">
+        <x:v>Damage</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4706,6 +4748,9 @@
       </x:c>
     </x:row>
     <x:row r="14">
+      <x:c r="A14" t="str">
+        <x:v>SingularityDelayedExplosionUniqueEffectSO</x:v>
+      </x:c>
       <x:c r="E14" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">SkillRange</x:t>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -1660,7 +1660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1706,6 +1706,21 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1940,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V88"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.3984375" customWidth="1"/>
@@ -5901,6 +5916,72 @@
         <v>93</v>
       </c>
     </row>
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="89" spans="1:22" ns1:dyDescent="0.4" ht="26.399999618530273" customHeight="1">
+      <c r="A89" t="inlineStr" s="21">
+        <is>
+          <t>UE_PhaseHarvesterWave</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr" s="21">
+        <is>
+          <t>공허 처형 파동</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr" s="21">
+        <is>
+          <t>PhaseHarvesterWaveUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr" s="22">
+        <is>
+          <t>Fighter 기본 공격 처치 시 그 위치에서 전방 {0}m, 폭 {1}m의 처형 파동을 방출합니다. 최대 {3}체에 치명타 없는 무속성 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr" s="21">
+        <is>
+          <t>6;2;60;6;1</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr" s="21">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G89" s="21">
+        <v>0</v>
+      </c>
+      <c r="H89" t="inlineStr" s="21">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I89" s="21">
+        <v>0</v>
+      </c>
+      <c r="K89" s="21">
+        <v>1</v>
+      </c>
+      <c r="T89" t="b" s="21">
+        <v>0</v>
+      </c>
+      <c r="U89" t="b" s="21">
+        <v>0</v>
+      </c>
+      <c r="V89" t="inlineStr" s="21">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+      <c r="J89" s="21"/>
+      <c r="L89" s="21"/>
+      <c r="M89" s="21"/>
+      <c r="N89" s="21"/>
+      <c r="O89" s="21"/>
+      <c r="P89" s="21"/>
+      <c r="Q89" s="21"/>
+      <c r="R89" s="21"/>
+      <c r="S89" s="21"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5909,7 +5990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6094,19 +6175,14 @@
         <v>510</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" spans="1:7" ns1:dyDescent="0.4">
       <c r="E15" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="E16" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="17" spans="5:5" x14ac:dyDescent="0.4">
-      <c r="E17" t="s">
-        <v>513</v>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PhaseHarvesterWaveUniqueEffectSO</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -1955,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V89"/>
+  <dimension ref="A1:V90"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.3984375" customWidth="1"/>
@@ -5982,6 +5982,48 @@
       <c r="R89" s="21"/>
       <c r="S89" s="21"/>
     </row>
+    <row r="90" spans="1:22" x14ac:dyDescent="0.4" ht="26.399999618530273" customHeight="1">
+      <c r="A90" t="str" s="21">
+        <v>UE_StarforgeBreachExplosion</v>
+      </c>
+      <c r="B90" t="str" s="21">
+        <v>스타 브리처 근접 폭발</v>
+      </c>
+      <c r="C90" t="str" s="21">
+        <v>StarBreacherExplosionUniqueEffectSO</v>
+      </c>
+      <c r="D90" s="22" t="str">
+        <v>거너 기본 산탄총 공격이 발사 원점에서 {0}m 이내의 적을 명중하면 그 피격 위치에 반경 {1}m 폭발을 일으킵니다. 최대 {3}체에 치명타 없는 화염 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</v>
+      </c>
+      <c r="E90" t="str" s="21">
+        <v>3;2.5;35;5;1.2</v>
+      </c>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="21"/>
+      <c r="K90" t="n" s="21">
+        <v>1.2</v>
+      </c>
+      <c r="T90" t="b" s="21">
+        <v>0</v>
+      </c>
+      <c r="U90" t="b" s="21">
+        <v>0</v>
+      </c>
+      <c r="V90" t="str" s="21">
+        <v>Auto</v>
+      </c>
+      <c r="J90" s="21"/>
+      <c r="L90" s="21"/>
+      <c r="M90" s="21"/>
+      <c r="N90" s="21"/>
+      <c r="O90" s="21"/>
+      <c r="P90" s="21"/>
+      <c r="Q90" s="21"/>
+      <c r="R90" s="21"/>
+      <c r="S90" s="21"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5990,7 +6032,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6185,6 +6227,14 @@
         </is>
       </c>
     </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="E16" t="s">
+        <v>512</v>
+      </c>
+      <c r="A16" t="str">
+        <v>StarBreacherExplosionUniqueEffectSO</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -1955,7 +1955,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V90"/>
+  <dimension ref="A1:V91"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.3984375" customWidth="1"/>
@@ -6024,6 +6024,58 @@
       <c r="R90" s="21"/>
       <c r="S90" s="21"/>
     </row>
+    <row r="91" spans="1:22" x14ac:dyDescent="0.4" ht="39.599998474121094" customHeight="1">
+      <c r="A91" s="21" t="str">
+        <v>UE_WasteHeatDischarge</v>
+      </c>
+      <c r="B91" s="21" t="str">
+        <v>폐열 방출</v>
+      </c>
+      <c r="C91" s="21" t="str">
+        <v>WasteHeatDischargeUniqueEffectSO</v>
+      </c>
+      <c r="D91" s="22" t="str">
+        <v>서로 다른 기본 공격이 적중할 때마다 열을 1씩 쌓아 최대 {0}까지 충전합니다. 충전 완료 후 다음 유효 기본 공격은 열을 모두 소비해 전방 {1}m·전체 각도 {2}° 범위의 적 최대 {4}체에게 공격력의 {3}%에 해당하는 치명타 없는 화염 피해를 추가로 줍니다. {5}초간 기본 공격이 적중하지 않으면 열이 사라집니다.</v>
+      </c>
+      <c r="E91" s="21" t="str">
+        <v>4;4;70;50;4;5</v>
+      </c>
+      <c r="F91" s="21" t="str"/>
+      <c r="G91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="21" t="str"/>
+      <c r="I91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="21" t="str"/>
+      <c r="K91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="21" t="str"/>
+      <c r="M91" s="21" t="str"/>
+      <c r="N91" s="21" t="str"/>
+      <c r="O91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R91" s="21" t="str"/>
+      <c r="S91" s="21" t="str"/>
+      <c r="T91" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U91" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V91" s="21" t="str">
+        <v>Auto</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6032,7 +6084,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6235,6 +6287,14 @@
         <v>StarBreacherExplosionUniqueEffectSO</v>
       </c>
     </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.4">
+      <c r="A17" t="str" s="0">
+        <v>WasteHeatDischargeUniqueEffectSO</v>
+      </c>
+      <c r="E17" t="s">
+        <v>513</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -1660,7 +1660,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1718,6 +1718,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1" vertical="top"/>
@@ -1955,7 +1958,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V91"/>
+  <dimension ref="A1:V102"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.3984375" customWidth="1"/>
@@ -5934,7 +5937,7 @@
       </c>
       <c r="D89" t="inlineStr" s="22">
         <is>
-          <t>Fighter 기본 공격 처치 시 그 위치에서 전방 {0}m, 폭 {1}m의 처형 파동을 방출합니다. 최대 {3}체에 치명타 없는 무속성 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</t>
+          <t>근접 기본 공격으로 처치 시 전방 {0}m·폭 {1}m의 파동을 방출합니다. 최대 {3}명에게 공격력의 {2}% 무속성 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr" s="21">
@@ -5992,8 +5995,10 @@
       <c r="C90" t="str" s="21">
         <v>StarBreacherExplosionUniqueEffectSO</v>
       </c>
-      <c r="D90" s="22" t="str">
-        <v>거너 기본 산탄총 공격이 발사 원점에서 {0}m 이내의 적을 명중하면 그 피격 위치에 반경 {1}m 폭발을 일으킵니다. 최대 {3}체에 치명타 없는 화염 피해 {2}%를 한 번 줍니다. 재사용 대기시간 {4}초.</v>
+      <c r="D90" s="22" t="inlineStr">
+        <is>
+          <t>{0}m 이내 산탄 적중 시 반경 {1}m에 폭발을 일으킵니다. 최대 {3}명에게 공격력의 {2}% 화염 피해를 주며 치명타는 없습니다. (쿨타임 {4}초)</t>
+        </is>
       </c>
       <c r="E90" t="str" s="21">
         <v>3;2.5;35;5;1.2</v>
@@ -6034,8 +6039,10 @@
       <c r="C91" s="21" t="str">
         <v>WasteHeatDischargeUniqueEffectSO</v>
       </c>
-      <c r="D91" s="22" t="str">
-        <v>서로 다른 기본 공격이 적중할 때마다 열을 1씩 쌓아 최대 {0}까지 충전합니다. 충전 완료 후 다음 유효 기본 공격은 열을 모두 소비해 전방 {1}m·전체 각도 {2}° 범위의 적 최대 {4}체에게 공격력의 {3}%에 해당하는 치명타 없는 화염 피해를 추가로 줍니다. {5}초간 기본 공격이 적중하지 않으면 열이 사라집니다.</v>
+      <c r="D91" s="22" t="inlineStr">
+        <is>
+          <t>기본 공격 {0}회 적중 후 다음 적중 시 화염을 방출합니다. 전방 {1}m·{2}° 내 최대 {4}명에게 공격력의 {3}% 추가 피해를 줍니다. 치명타는 없으며 {5}초간 미적중 시 충전이 초기화됩니다.</t>
+        </is>
       </c>
       <c r="E91" s="21" t="str">
         <v>4;4;70;50;4;5</v>
@@ -6074,6 +6081,638 @@
       </c>
       <c r="V91" s="21" t="str">
         <v>Auto</v>
+      </c>
+    </row>
+    <row r="92" ht="48" customHeight="1">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>UE_SunfallBurnField</t>
+        </is>
+      </c>
+      <c r="B92" s="21" t="inlineStr">
+        <is>
+          <t>일식 점화</t>
+        </is>
+      </c>
+      <c r="C92" s="21" t="inlineStr">
+        <is>
+          <t>SunfallBurnFieldUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D92" s="23" t="inlineStr">
+        <is>
+          <t>유탄 충돌 시 반경 {0}m에 {1}초간 화상 지대를 남깁니다. {2}초마다 화상을 갱신하며 최대 {3}개까지 유지합니다.</t>
+        </is>
+      </c>
+      <c r="E92" s="21" t="inlineStr">
+        <is>
+          <t>3;4;0.5;2</t>
+        </is>
+      </c>
+      <c r="G92" s="21">
+        <v>0</v>
+      </c>
+      <c r="H92" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I92" s="21">
+        <v>0</v>
+      </c>
+      <c r="K92" s="21">
+        <v>0</v>
+      </c>
+      <c r="L92" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T92" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U92" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V92" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="48" customHeight="1">
+      <c r="A93" s="21" t="inlineStr">
+        <is>
+          <t>UE_CrusaderCriticalChain</t>
+        </is>
+      </c>
+      <c r="B93" s="21" t="inlineStr">
+        <is>
+          <t>성스러운 일격</t>
+        </is>
+      </c>
+      <c r="C93" s="21" t="inlineStr">
+        <is>
+          <t>ChainLightningUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D93" s="23" t="inlineStr">
+        <is>
+          <t>기본 공격 치명타 시 {1}m 내 다른 적 최대 {0}명에게 공격력의 {2}% 전기 피해를 연쇄로 줍니다. 다음 대상마다 피해가 {3}%로 줄어듭니다. (쿨타임 {4}초)</t>
+        </is>
+      </c>
+      <c r="E93" s="21" t="inlineStr">
+        <is>
+          <t>2;4;50;70;1.5</t>
+        </is>
+      </c>
+      <c r="G93" s="21">
+        <v>0</v>
+      </c>
+      <c r="H93" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I93" s="21">
+        <v>0</v>
+      </c>
+      <c r="J93" s="21" t="inlineStr">
+        <is>
+          <t>OnCrit</t>
+        </is>
+      </c>
+      <c r="K93" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="L93" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T93" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U93" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V93" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="48" customHeight="1">
+      <c r="A94" s="21" t="inlineStr">
+        <is>
+          <t>UE_GuardiansJusticeShield</t>
+        </is>
+      </c>
+      <c r="B94" s="21" t="inlineStr">
+        <is>
+          <t>정의는 승리한다</t>
+        </is>
+      </c>
+      <c r="C94" s="21" t="inlineStr">
+        <is>
+          <t>GuardiansJusticeShieldUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D94" s="23" t="inlineStr">
+        <is>
+          <t>피격으로 잃은 체력의 {0}%를 최대 체력의 {1}%까지 저장합니다. 첫 피격 후 {2}초 내 기본 공격 적중 시 {3}초 보호막으로 전환합니다. (쿨타임 {4}초)</t>
+        </is>
+      </c>
+      <c r="E94" s="21" t="inlineStr">
+        <is>
+          <t>50;12;5;5;8</t>
+        </is>
+      </c>
+      <c r="G94" s="21">
+        <v>0</v>
+      </c>
+      <c r="H94" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I94" s="21">
+        <v>0</v>
+      </c>
+      <c r="K94" s="21">
+        <v>8</v>
+      </c>
+      <c r="L94" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T94" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U94" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V94" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="48" customHeight="1">
+      <c r="A95" s="21" t="inlineStr">
+        <is>
+          <t>UE_NinjaDodgeAttack</t>
+        </is>
+      </c>
+      <c r="B95" s="21" t="inlineStr">
+        <is>
+          <t>그림자 보법</t>
+        </is>
+      </c>
+      <c r="C95" s="21" t="inlineStr">
+        <is>
+          <t>NinjaDodgeAttackUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D95" s="23" t="inlineStr">
+        <is>
+          <t>회피 후 {1}초 내 다음 기본 공격의 피해가 {0}% 증가합니다. 빗나가도 소모됩니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+      <c r="E95" s="21" t="inlineStr">
+        <is>
+          <t>20;3;6</t>
+        </is>
+      </c>
+      <c r="G95" s="21">
+        <v>0</v>
+      </c>
+      <c r="H95" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I95" s="21">
+        <v>0</v>
+      </c>
+      <c r="K95" s="21">
+        <v>6</v>
+      </c>
+      <c r="L95" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T95" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U95" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V95" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="48" customHeight="1">
+      <c r="A96" s="21" t="inlineStr">
+        <is>
+          <t>UE_AntimatterPiercingShot</t>
+        </is>
+      </c>
+      <c r="B96" s="21" t="inlineStr">
+        <is>
+          <t>집속 사격</t>
+        </is>
+      </c>
+      <c r="C96" s="21" t="inlineStr">
+        <is>
+          <t>AntimatterPiercingShotUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>기본 사격이 최대 {0}명을 관통합니다. 두 번째·세 번째 적에게 기본 피해의 {1}%·{2}% 피해를 줍니다. 후속 피해는 치명타가 없으며 벽은 관통하지 못합니다.</t>
+        </is>
+      </c>
+      <c r="E96" s="21" t="inlineStr">
+        <is>
+          <t>3;70;50</t>
+        </is>
+      </c>
+      <c r="G96" s="21">
+        <v>0</v>
+      </c>
+      <c r="H96" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I96" s="21">
+        <v>0</v>
+      </c>
+      <c r="K96" s="21">
+        <v>0</v>
+      </c>
+      <c r="L96" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T96" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U96" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V96" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="21" t="inlineStr">
+        <is>
+          <t>UE_EchoVaultReplay</t>
+        </is>
+      </c>
+      <c r="B97" s="21" t="inlineStr">
+        <is>
+          <t>충격파 축적</t>
+        </is>
+      </c>
+      <c r="C97" s="21" t="inlineStr">
+        <is>
+          <t>EchoVaultReplayUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D97" s="23" t="inlineStr">
+        <is>
+          <t>산탄 발사 {0}초 후 같은 위치·방향에서 최대 {2}명에게 공격력의 {1}% 추가 피해를 줍니다. 치명타는 없으며 동시 최대 {4}회까지 예약합니다. (쿨타임 {3}초)</t>
+        </is>
+      </c>
+      <c r="E97" s="21" t="inlineStr">
+        <is>
+          <t>0.45;35;6;1.5;2</t>
+        </is>
+      </c>
+      <c r="G97" s="21">
+        <v>0</v>
+      </c>
+      <c r="H97" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I97" s="21">
+        <v>0</v>
+      </c>
+      <c r="K97" s="21">
+        <v>1.5</v>
+      </c>
+      <c r="L97" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T97" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U97" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V97" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="48" customHeight="1">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>UE_WorldEnderChargedBlast</t>
+        </is>
+      </c>
+      <c r="B98" s="21" t="inlineStr">
+        <is>
+          <t>종말 포격</t>
+        </is>
+      </c>
+      <c r="C98" s="21" t="inlineStr">
+        <is>
+          <t>WorldEnderChargedBlastUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D98" s="23" t="inlineStr">
+        <is>
+          <t>{0}초 충전 후 다음 유탄 충돌 시 반경 {1}m 내 최대 {3}명에게 공격력의 {2}% 추가 폭발 피해를 줍니다. 치명타는 없습니다.</t>
+        </is>
+      </c>
+      <c r="E98" s="21" t="inlineStr">
+        <is>
+          <t>8;5;150;8</t>
+        </is>
+      </c>
+      <c r="G98" s="21">
+        <v>0</v>
+      </c>
+      <c r="H98" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I98" s="21">
+        <v>0</v>
+      </c>
+      <c r="K98" s="21">
+        <v>0</v>
+      </c>
+      <c r="L98" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T98" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U98" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V98" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="48" customHeight="1">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>UE_CoreBreakerArmorBreak</t>
+        </is>
+      </c>
+      <c r="B99" s="21" t="inlineStr">
+        <is>
+          <t>코어 노출</t>
+        </is>
+      </c>
+      <c r="C99" s="21" t="inlineStr">
+        <is>
+          <t>CoreBreakerExposeUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다.</t>
+        </is>
+      </c>
+      <c r="E99" s="21" t="inlineStr">
+        <is>
+          <t>3;3;4;20;10</t>
+        </is>
+      </c>
+      <c r="G99" s="21">
+        <v>0</v>
+      </c>
+      <c r="H99" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I99" s="21">
+        <v>0</v>
+      </c>
+      <c r="K99" s="21">
+        <v>0</v>
+      </c>
+      <c r="L99" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T99" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U99" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V99" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="48" customHeight="1">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>UE_SuperRefrigerantFreeze</t>
+        </is>
+      </c>
+      <c r="B100" s="21" t="inlineStr">
+        <is>
+          <t>열 강탈</t>
+        </is>
+      </c>
+      <c r="C100" s="21" t="inlineStr">
+        <is>
+          <t>SuperRefrigerantFreezeUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D100" s="23" t="inlineStr">
+        <is>
+          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다.</t>
+        </is>
+      </c>
+      <c r="E100" s="21" t="inlineStr">
+        <is>
+          <t>3;3;1;85;0.6;5</t>
+        </is>
+      </c>
+      <c r="G100" s="21">
+        <v>0</v>
+      </c>
+      <c r="H100" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I100" s="21">
+        <v>0</v>
+      </c>
+      <c r="K100" s="21">
+        <v>0</v>
+      </c>
+      <c r="L100" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T100" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U100" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V100" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>UE_WildfireSpread</t>
+        </is>
+      </c>
+      <c r="B101" s="21" t="inlineStr">
+        <is>
+          <t>되살아나는 불씨</t>
+        </is>
+      </c>
+      <c r="C101" s="21" t="inlineStr">
+        <is>
+          <t>WildfireSpreadUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D101" s="23" t="inlineStr">
+        <is>
+          <t>이 무기의 화상이 남은 적 처치 시 {0}m 내 최대 {1}명에게 화상을 옮깁니다. 전파된 화상은 다시 전파되지 않습니다. (쿨타임 {2}초)</t>
+        </is>
+      </c>
+      <c r="E101" s="21" t="inlineStr">
+        <is>
+          <t>4;3;1</t>
+        </is>
+      </c>
+      <c r="G101" s="21">
+        <v>0</v>
+      </c>
+      <c r="H101" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I101" s="21">
+        <v>0</v>
+      </c>
+      <c r="K101" s="21">
+        <v>1</v>
+      </c>
+      <c r="L101" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T101" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U101" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V101" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="48" customHeight="1">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>UE_SmileSignalMark</t>
+        </is>
+      </c>
+      <c r="B102" s="21" t="inlineStr">
+        <is>
+          <t>기분 전환</t>
+        </is>
+      </c>
+      <c r="C102" s="21" t="inlineStr">
+        <is>
+          <t>SmileSignalMarkUniqueEffectSO</t>
+        </is>
+      </c>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>기본 사격 시 {0}초간 표식을 남깁니다. 아군의 다음 기본 공격이 표식을 소모해 공격자 공격력의 {1}% 추가 피해를 줍니다. 치명타는 없으며 혼자면 직접 소모합니다. 최대 {2}개, 재부여 대기시간은 {3}초입니다.</t>
+        </is>
+      </c>
+      <c r="E102" s="21" t="inlineStr">
+        <is>
+          <t>3;25;3;1</t>
+        </is>
+      </c>
+      <c r="G102" s="21">
+        <v>0</v>
+      </c>
+      <c r="H102" s="21" t="inlineStr">
+        <is>
+          <t>Ignore</t>
+        </is>
+      </c>
+      <c r="I102" s="21">
+        <v>0</v>
+      </c>
+      <c r="K102" s="21">
+        <v>0</v>
+      </c>
+      <c r="L102" s="21" t="inlineStr">
+        <is>
+          <t>ShareCooldown</t>
+        </is>
+      </c>
+      <c r="T102" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="U102" s="21" t="b">
+        <v>0</v>
+      </c>
+      <c r="V102" s="21" t="inlineStr">
+        <is>
+          <t>Auto</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -6084,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -6295,6 +6934,76 @@
         <v>513</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t>SunfallBurnFieldUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>GuardiansJusticeShieldUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t>NinjaDodgeAttackUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="inlineStr">
+        <is>
+          <t>AntimatterPiercingShotUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>EchoVaultReplayUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>WorldEnderChargedBlastUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>CoreBreakerExposeUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="0" t="inlineStr">
+        <is>
+          <t>SuperRefrigerantFreezeUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="0" t="inlineStr">
+        <is>
+          <t>WildfireSpreadUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="0" t="inlineStr">
+        <is>
+          <t>SmileSignalMarkUniqueEffectSO</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -2635,8 +2635,10 @@
       <c r="C14" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="1" t="s">
-        <v>96</v>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 100회 중첩되며 공격력은 최대 50% 증가합니다.</t>
+        </is>
       </c>
       <c r="E14" s="12">
         <v>0.5</v>
@@ -6505,7 +6507,7 @@
       </c>
       <c r="D99" s="23" t="inlineStr">
         <is>
-          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다.</t>
+          <t>{1}초 내 같은 적에게 기본 공격을 {0}회 적중시키면 {2}초간 방어력을 {3}% 낮춥니다. 보스는 {4}% 감소하며 중첩되지 않습니다. 다른 적을 적중시키면 누적 적중 횟수가 초기화됩니다.</t>
         </is>
       </c>
       <c r="E99" s="21" t="inlineStr">
@@ -6562,7 +6564,7 @@
       </c>
       <c r="D100" s="23" t="inlineStr">
         <is>
-          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다.</t>
+          <t>기본 공격 시 {2}초간 적의 이동 속도를 {3}%로 낮춥니다. {1}초 내 같은 적에게 {0}회 적중하면 {4}초간 빙결합니다. 대상별 빙결 쿨타임은 {5}초이며 보스는 감속만 적용합니다. 다른 적을 적중시키면 누적 적중 횟수가 초기화됩니다.</t>
         </is>
       </c>
       <c r="E100" s="21" t="inlineStr">

--- a/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
+++ b/Assets/Resources/DataFiles/ItemData/1. ExcelFile/UniqueEffectTable.xlsx
@@ -1272,12 +1272,12 @@
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F11" s="23" t="inlineStr">
         <is>
-          <t>attackPowerPercent:45</t>
+          <t>attackPowerPercent:35</t>
         </is>
       </c>
       <c r="G11" s="23" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="D14" s="23" t="inlineStr">
         <is>
-          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 100회 중첩되며 공격력은 최대 50% 증가합니다.</t>
+          <t>적을 처치할 때마다 공격력이 {0}% 증가합니다. 최대 40회 중첩되며 공격력은 최대 20% 증가합니다.</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>35;15</t>
+          <t>25;15</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>attackPowerPercent:35;defensePowerPercent:-15</t>
+          <t>attackPowerPercent:25;defensePowerPercent:-15</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>40;25;10</t>
+          <t>10;20;10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>attackPowerPercent:40;fireBonusFlat:25;defensePowerPercent:-10</t>
+          <t>attackPowerPercent:10;fireBonusFlat:20;defensePowerPercent:-10</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>15;15</t>
+          <t>30;15</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>critRateFlat:15;skillRangePercent:15</t>
+          <t>critRateFlat:30;skillRangePercent:15</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>15;20;6</t>
+          <t>5;15;6</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>attackPowerPercent:15;fireBonusFlat:20;defensePowerPercent:-6</t>
+          <t>attackPowerPercent:5;fireBonusFlat:15;defensePowerPercent:-6</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>4;5;40;80;0.6</t>
+          <t>4;5;80;80;0.5</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -4141,7 +4141,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -4314,7 +4314,7 @@
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4341,7 @@
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>4.5;6;55;0.5;3</t>
+          <t>4.5;6;60;0.5;3</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="E89" s="21" t="inlineStr">
         <is>
-          <t>8;2.5;90;8;1</t>
+          <t>8;2.5;200;8;1</t>
         </is>
       </c>
       <c r="F89" s="21" t="inlineStr"/>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="E90" s="21" t="inlineStr">
         <is>
-          <t>3.5;3;55;6;1</t>
+          <t>3.5;3;80;6;1</t>
         </is>
       </c>
       <c r="F90" s="21" t="n"/>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E91" s="21" t="inlineStr">
         <is>
-          <t>3;5;90;90;6;5</t>
+          <t>3;5;90;130;6;5</t>
         </is>
       </c>
       <c r="F91" s="21" t="str"/>
@@ -6342,7 +6342,7 @@
       </c>
       <c r="E93" s="21" t="inlineStr">
         <is>
-          <t>3;5;70;80;1</t>
+          <t>4;5;180;80;0.4</t>
         </is>
       </c>
       <c r="G93" s="21" t="n">
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="K93" s="21" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="L93" s="21" t="inlineStr">
         <is>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="E96" s="21" t="inlineStr">
         <is>
-          <t>3;90;75</t>
+          <t>3;100;100</t>
         </is>
       </c>
       <c r="G96" s="21" t="n">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="E97" s="21" t="inlineStr">
         <is>
-          <t>0.45;55;8;1.2;2</t>
+          <t>0.45;70;8;1.2;2</t>
         </is>
       </c>
       <c r="G97" s="21" t="n">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="E99" s="21" t="inlineStr">
         <is>
-          <t>3;3;5;35;20</t>
+          <t>3;3;5;45;25</t>
         </is>
       </c>
       <c r="G99" s="21" t="n">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E101" s="21" t="inlineStr">
         <is>
-          <t>5;5;0.8</t>
+          <t>6;8;0.3</t>
         </is>
       </c>
       <c r="G101" s="21" t="n">
@@ -6818,7 +6818,7 @@
         <v>0</v>
       </c>
       <c r="K101" s="21" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="L101" s="21" t="inlineStr">
         <is>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="E102" s="21" t="inlineStr">
         <is>
-          <t>4;40;4;1</t>
+          <t>4;100;4;1</t>
         </is>
       </c>
       <c r="G102" s="21" t="n">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>화상·빙결·감전 중 서로 다른 두 가지가 걸린 적을 적중하면 반경 {0}m에 공격력 {1}%의 무속성 폭발을 일으킵니다. (대상별 {2}초, 최대 {3}명)</t>
+          <t>화상·빙결·감전 중 하나라도 걸린 적을 적중하면 반경 {0}m에 공격력 {1}%의 무속성 폭발을 일으킵니다. 서로 다른 두 가지가 걸려 있으면 폭발 피해가 50% 증가합니다. (대상별 {2}초, 최대 {3}명)</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>3;100;3;8</t>
+          <t>3;60;2;6</t>
         </is>
       </c>
       <c r="G118" t="n">
